--- a/R/salidas/TDF_discretas.xlsx
+++ b/R/salidas/TDF_discretas.xlsx
@@ -45,34 +45,34 @@
     <t xml:space="preserve">Hi_dsc</t>
   </si>
   <si>
-    <t xml:space="preserve">[   1930-   1940[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[   1940-   1950[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[   1950-   1960[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[   1960-   1970[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[   1970-   1980[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[   1980-   1990[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[   1990-   2000[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[   2000-   2010[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[   2010-   2020[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[   2020-   2030[</t>
+    <t xml:space="preserve">[1930-1940[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1940-1950[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1950-1960[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1960-1970[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1970-1980[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1980-1990[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[1990-2000[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2000-2010[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2010-2020[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[2020-2030[</t>
   </si>
   <si>
     <t xml:space="preserve">indicador</t>
@@ -123,52 +123,52 @@
     <t xml:space="preserve">Moda</t>
   </si>
   <si>
-    <t xml:space="preserve">[0-      5[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[      5-     10[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[     10-     15[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[     15-     20[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[     20-     25[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[     25-     30[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[     30-     35[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[     35-     40[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[     40-     45[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[     45-     50[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[     50-     55[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[     55-     60[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[     60-     65[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[     65-     70[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[     70-     75[</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[     75-     80[</t>
+    <t xml:space="preserve">[0-5[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[5-10[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[10-15[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[15-20[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[20-25[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[25-30[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[30-35[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[35-40[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[40-45[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[45-50[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[50-55[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[55-60[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[60-65[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[65-70[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[70-75[</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[75-80[</t>
   </si>
 </sst>
 </file>
